--- a/data/players.xlsx
+++ b/data/players.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>May2026_score</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,9 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
+      <c r="H2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +530,9 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +562,9 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +594,9 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
+      <c r="H5" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +626,9 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
+      <c r="H6" t="n">
+        <v>396</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +658,9 @@
       <c r="G7" t="n">
         <v>16.5</v>
       </c>
+      <c r="H7" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +690,9 @@
       <c r="G8" t="n">
         <v>6</v>
       </c>
+      <c r="H8" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +722,9 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
+      <c r="H9" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +754,9 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +786,9 @@
       <c r="G11" t="n">
         <v>47</v>
       </c>
+      <c r="H11" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +818,9 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
+      <c r="H12" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +850,9 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
+      <c r="H13" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +882,9 @@
       <c r="G14" t="n">
         <v>26</v>
       </c>
+      <c r="H14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +914,9 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
+      <c r="H15" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +946,9 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +978,9 @@
       <c r="G17" t="n">
         <v>1</v>
       </c>
+      <c r="H17" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1010,9 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1042,9 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
+      <c r="H19" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1074,9 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
+      <c r="H20" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1106,9 @@
       <c r="G21" t="n">
         <v>30</v>
       </c>
+      <c r="H21" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1138,9 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
+      <c r="H22" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1170,9 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1202,9 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1234,9 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
+      <c r="H25" t="n">
+        <v>482</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1266,9 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
+      <c r="H26" t="n">
+        <v>262</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1298,9 @@
       <c r="G27" t="n">
         <v>39</v>
       </c>
+      <c r="H27" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1330,9 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1362,9 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
+      <c r="H29" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1394,9 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1426,9 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1458,9 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1490,9 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
+      <c r="H33" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1522,9 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1554,9 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
+      <c r="H35" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1586,9 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
+      <c r="H36" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1618,9 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1650,9 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
+      <c r="H38" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1682,9 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
+      <c r="H39" t="n">
+        <v>244</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1594,6 +1713,9 @@
       </c>
       <c r="G40" t="n">
         <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="41">
@@ -1614,6 +1736,9 @@
       <c r="G41" t="n">
         <v>392</v>
       </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1643,6 +1768,9 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
+      <c r="H42" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1672,6 +1800,9 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
+      <c r="H43" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1701,6 +1832,9 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
+      <c r="H44" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1728,6 +1862,9 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1749,6 +1886,9 @@
       <c r="G46" t="n">
         <v>392</v>
       </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1776,6 +1916,9 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1797,6 +1940,9 @@
       <c r="G48" t="n">
         <v>392</v>
       </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1824,6 +1970,9 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/players.xlsx
+++ b/data/players.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>May2026</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>June2026_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +506,9 @@
       <c r="H2" t="n">
         <v>81</v>
       </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -533,6 +541,9 @@
       <c r="H3" t="n">
         <v>0</v>
       </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,6 +576,9 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +609,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>132</v>
+        <v>387</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -627,7 +644,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>396</v>
+        <v>555</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -659,7 +679,10 @@
         <v>16.5</v>
       </c>
       <c r="H7" t="n">
-        <v>384</v>
+        <v>588</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +714,10 @@
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>162</v>
+        <v>176</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -725,6 +751,9 @@
       <c r="H9" t="n">
         <v>22</v>
       </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -755,7 +784,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +819,10 @@
         <v>47</v>
       </c>
       <c r="H11" t="n">
-        <v>222</v>
+        <v>246</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -821,6 +856,9 @@
       <c r="H12" t="n">
         <v>26</v>
       </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -853,6 +891,9 @@
       <c r="H13" t="n">
         <v>40</v>
       </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -883,7 +924,10 @@
         <v>26</v>
       </c>
       <c r="H14" t="n">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -917,6 +961,9 @@
       <c r="H15" t="n">
         <v>44</v>
       </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -949,6 +996,9 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -981,6 +1031,9 @@
       <c r="H17" t="n">
         <v>64</v>
       </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1013,6 +1066,9 @@
       <c r="H18" t="n">
         <v>0</v>
       </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1045,6 +1101,9 @@
       <c r="H19" t="n">
         <v>52</v>
       </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1077,6 +1136,9 @@
       <c r="H20" t="n">
         <v>66</v>
       </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1109,6 +1171,9 @@
       <c r="H21" t="n">
         <v>154</v>
       </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1141,6 +1206,9 @@
       <c r="H22" t="n">
         <v>94</v>
       </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1173,6 +1241,9 @@
       <c r="H23" t="n">
         <v>0</v>
       </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1205,6 +1276,9 @@
       <c r="H24" t="n">
         <v>0</v>
       </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1235,7 +1309,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>482</v>
+        <v>546</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1267,7 +1344,10 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>262</v>
+        <v>272</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1299,7 +1379,10 @@
         <v>39</v>
       </c>
       <c r="H27" t="n">
-        <v>148</v>
+        <v>204</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1333,6 +1416,9 @@
       <c r="H28" t="n">
         <v>0</v>
       </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1365,6 +1451,9 @@
       <c r="H29" t="n">
         <v>12</v>
       </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1397,6 +1486,9 @@
       <c r="H30" t="n">
         <v>0</v>
       </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1429,6 +1521,9 @@
       <c r="H31" t="n">
         <v>0</v>
       </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1461,6 +1556,9 @@
       <c r="H32" t="n">
         <v>0</v>
       </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1493,6 +1591,9 @@
       <c r="H33" t="n">
         <v>132</v>
       </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1525,6 +1626,9 @@
       <c r="H34" t="n">
         <v>0</v>
       </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1557,6 +1661,9 @@
       <c r="H35" t="n">
         <v>280</v>
       </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1589,6 +1696,9 @@
       <c r="H36" t="n">
         <v>28</v>
       </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1621,6 +1731,9 @@
       <c r="H37" t="n">
         <v>0</v>
       </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1653,6 +1766,9 @@
       <c r="H38" t="n">
         <v>136</v>
       </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1685,6 +1801,9 @@
       <c r="H39" t="n">
         <v>244</v>
       </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1716,6 +1835,9 @@
       </c>
       <c r="H40" t="n">
         <v>184</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1739,6 +1861,9 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1771,6 +1896,9 @@
       <c r="H42" t="n">
         <v>80</v>
       </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1803,6 +1931,9 @@
       <c r="H43" t="n">
         <v>92</v>
       </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1835,6 +1966,9 @@
       <c r="H44" t="n">
         <v>24</v>
       </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1865,6 +1999,9 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1889,6 +2026,9 @@
       <c r="H46" t="n">
         <v>0</v>
       </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1919,6 +2059,9 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,6 +2086,9 @@
       <c r="H48" t="n">
         <v>0</v>
       </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1973,6 +2119,9 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>0</v>
       </c>
     </row>
